--- a/results/Int All Data -0.5/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_8_permute.xlsx
@@ -440,1543 +440,1543 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8374136409360943</v>
+        <v>0.8370478802487648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8371336857289274</v>
+        <v>0.8375472918683293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8371336857289274</v>
+        <v>0.8409320610397252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8368410771790638</v>
+        <v>0.8417114278664566</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8381803544201289</v>
+        <v>0.842697597762889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8351613459360627</v>
+        <v>0.842223492828718</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8313503172825681</v>
+        <v>0.8402511530358532</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8315697736949659</v>
+        <v>0.8402511530358532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8310098632806322</v>
+        <v>0.8402511530358532</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.831362970625265</v>
+        <v>0.8404579561055542</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8301573443164347</v>
+        <v>0.8388640303427157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8260311683463979</v>
+        <v>0.8328612054839588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8270173382428303</v>
+        <v>0.8318145367927572</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8309620178285599</v>
+        <v>0.8315950803803595</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8289291792409259</v>
+        <v>0.8306820626213931</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8289291792409259</v>
+        <v>0.8272972934499971</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8289291792409259</v>
+        <v>0.8185229911236801</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8270299915855271</v>
+        <v>0.8180840782988846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8282834633464295</v>
+        <v>0.8215139250036378</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8282834633464295</v>
+        <v>0.8208935157945351</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8307552147588588</v>
+        <v>0.8212466231391677</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8315950803803595</v>
+        <v>0.8218796856909674</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8299153491373583</v>
+        <v>0.8160864318206262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8298675036852861</v>
+        <v>0.816706841029729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8284198821973795</v>
+        <v>0.8170599483743618</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.827373213506178</v>
+        <v>0.8175467066512296</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8311715888169757</v>
+        <v>0.8224902094760884</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8308058281296462</v>
+        <v>0.8224902094760884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8329244721974427</v>
+        <v>0.8250224596832869</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8314388906814458</v>
+        <v>0.8262632781014925</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8331312752671437</v>
+        <v>0.8269568394480612</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8314515440241426</v>
+        <v>0.8287350295139218</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8319861477530827</v>
+        <v>0.8273226001353908</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8319129956156167</v>
+        <v>0.8276025553425577</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8332522728566819</v>
+        <v>0.8301348055497562</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8341526372729515</v>
+        <v>0.8203237199562194</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8375374064443475</v>
+        <v>0.8194838543347189</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8113805745882918</v>
+        <v>0.8195570064721848</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8135850241362512</v>
+        <v>0.8195570064721848</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8128056573095197</v>
+        <v>0.8181445770936537</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8158978179310519</v>
+        <v>0.8196906574044198</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8162382719329879</v>
+        <v>0.8181572304363505</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8122330935524893</v>
+        <v>0.8191434003327829</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8155925560384916</v>
+        <v>0.8201900690239844</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8155925560384916</v>
+        <v>0.8154055238167544</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8153126008313246</v>
+        <v>0.8201900690239844</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8193051258691264</v>
+        <v>0.8196301586096507</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8189520185244937</v>
+        <v>0.8196428119523476</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8160061621778933</v>
+        <v>0.8203616799843099</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8157993591081925</v>
+        <v>0.8179025819145773</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8157262069707265</v>
+        <v>0.8224676707094096</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8244048183928989</v>
+        <v>0.8211283934683444</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8211790068391318</v>
+        <v>0.81150157217783</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8229192368769019</v>
+        <v>0.8093350826579612</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8231991920840689</v>
+        <v>0.8082884139667597</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8231991920840689</v>
+        <v>0.8103085992116967</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8226266283270383</v>
+        <v>0.8100610681951905</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8204249466977939</v>
+        <v>0.8157206711332967</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8195850810762932</v>
+        <v>0.8124217074420634</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8185384123850918</v>
+        <v>0.8124217074420634</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8177716989010573</v>
+        <v>0.8146135036473261</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8186115645225578</v>
+        <v>0.8149666109919588</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8233708030443943</v>
+        <v>0.804421236105048</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8233708030443943</v>
+        <v>0.8056268624138782</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8233708030443943</v>
+        <v>0.7952530984872929</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8226519350124319</v>
+        <v>0.787825190907308</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8156700577625093</v>
+        <v>0.7784980956719241</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8061432769626916</v>
+        <v>0.7826017328752823</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8141283270382953</v>
+        <v>0.779862679598383</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8052274912850101</v>
+        <v>0.788092492771778</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8029878496276754</v>
+        <v>0.7766269826206338</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.805984319345063</v>
+        <v>0.7690274640803234</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8047181942414637</v>
+        <v>0.7675545359070233</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8019214100885101</v>
+        <v>0.7675545359070233</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7969174084688824</v>
+        <v>0.7694537235624221</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.797076366086511</v>
+        <v>0.7698926363872176</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7919513668773448</v>
+        <v>0.7734363631762421</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7983298378474133</v>
+        <v>0.7385870803044394</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8084026894679902</v>
+        <v>0.7400572405590247</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8026545131310063</v>
+        <v>0.7320947292500997</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8040064437147683</v>
+        <v>0.7320947292500997</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8044932019916362</v>
+        <v>0.7403822732995489</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8044932019916362</v>
+        <v>0.7377009508987036</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8046521596092648</v>
+        <v>0.7128470179234599</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8055651773682313</v>
+        <v>0.7011466300985063</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.803153924750571</v>
+        <v>0.7069904973396347</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7975927806353243</v>
+        <v>0.7058607910869854</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7913578460214727</v>
+        <v>0.7213370154560581</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7914183448162418</v>
+        <v>0.7185853088364619</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7914183448162418</v>
+        <v>0.7185853088364619</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7876678149575165</v>
+        <v>0.7190720671133297</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7955824808143691</v>
+        <v>0.7309721405027173</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7809587754094938</v>
+        <v>0.6800713015860965</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7662041869910984</v>
+        <v>0.6450954852873259</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7655232789872264</v>
+        <v>0.6664733077735812</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7721591663977831</v>
+        <v>0.6631589228209362</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7668625562282916</v>
+        <v>0.6701831096855011</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7545670658796287</v>
+        <v>0.6754797198549927</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7424629573392552</v>
+        <v>0.6044181518527657</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7467128988175451</v>
+        <v>0.6032829097626866</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7495630642600009</v>
+        <v>0.6032829097626866</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7523147708795971</v>
+        <v>0.6032829097626866</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7432395562472716</v>
+        <v>0.594417266118777</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7373098835259805</v>
+        <v>0.5851253629927686</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7377108363226855</v>
+        <v>0.5888731249327791</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7445788334883368</v>
+        <v>0.5888731249327791</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7483953979792611</v>
+        <v>0.5750260184359203</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7439837309646276</v>
+        <v>0.5482982044906713</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7088220686949975</v>
+        <v>0.5489312670424709</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6992980558138946</v>
+        <v>0.5472993812515421</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6922485622639361</v>
+        <v>0.5413317485021606</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6960821296841093</v>
+        <v>0.5422447662611271</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6883616135542607</v>
+        <v>0.5424389159881312</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6334623183454489</v>
+        <v>0.5619863533699015</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6063786291368523</v>
+        <v>0.5565181322400845</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.612181373014216</v>
+        <v>0.5543994881722879</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6226282890782673</v>
+        <v>0.5540210741422615</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6528365630990567</v>
+        <v>0.5547272888315271</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6469575037485528</v>
+        <v>0.5547272888315271</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6537369275153264</v>
+        <v>0.5663952524658201</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6573031930710296</v>
+        <v>0.5674419211570216</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6303432693706861</v>
+        <v>0.5763933702810941</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6319976939282935</v>
+        <v>0.5841166543296575</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6671676599540683</v>
+        <v>0.5682592480118436</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6602870094457203</v>
+        <v>0.5658958408462555</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5894085194956378</v>
+        <v>0.5720224312132658</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5914808997791992</v>
+        <v>0.5655779256109983</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5970645826611245</v>
+        <v>0.5532290539728333</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5952709713338521</v>
+        <v>0.5486991572873764</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6005576960793617</v>
+        <v>0.5546414833513644</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5645478644320863</v>
+        <v>0.5397884361101094</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5645478644320863</v>
+        <v>0.5446334801121087</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5219389191514668</v>
+        <v>0.5509894123154985</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5237902613547935</v>
+        <v>0.5344890580219029</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5171092964108793</v>
+        <v>0.5076853240204732</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5139285623904695</v>
+        <v>0.5076853240204732</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.498984173831622</v>
+        <v>0.5082452344348068</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4991051714211602</v>
+        <v>0.5039221408190508</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4998718849051949</v>
+        <v>0.5039221408190508</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5000786879748957</v>
+        <v>0.5041415972314486</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5000786879748957</v>
+        <v>0.5007188680319624</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4999197303572671</v>
+        <v>0.5007188680319624</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4989687525702102</v>
+        <v>0.5007188680319624</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.500537371647655</v>
+        <v>0.4997931969302991</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5001842643030222</v>
+        <v>0.4997931969302991</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5014982348586938</v>
+        <v>0.5000731521374659</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5007793668267315</v>
+        <v>0.5000731521374659</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5004262594820987</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5001463042749318</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5001463042749318</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5001463042749318</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5001463042749318</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5002926085498637</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5002926085498637</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
